--- a/data/trans_dic/IP07_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP07_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>75,87%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>64,12%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69,17%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75,34%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>78,8%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>72,03%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>67,77%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>70,92%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>75,87%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>64,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,17%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,4; 86,9</t>
+          <t>65,9; 83,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,6; 80,2</t>
+          <t>52,84; 72,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,78; 76,26</t>
+          <t>58,69; 78,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,17; 81,21</t>
+          <t>65,6; 83,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,55; 83,85</t>
+          <t>68,87; 86,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,91; 74,15</t>
+          <t>62,38; 80,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,4; 77,57</t>
+          <t>57,89; 77,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67,85; 84,22</t>
+          <t>63,03; 81,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70,33; 83,1</t>
+          <t>71,21; 83,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61,08; 75,07</t>
+          <t>60,77; 75,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61,28; 74,61</t>
+          <t>61,73; 75,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,15; 80,93</t>
+          <t>67,04; 80,07</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75,98%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>77,88%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85,07%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80,19%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>75,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>74,03%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>90,29%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>82,64%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>75,98%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>77,88%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>85,07%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,18; 81,65</t>
+          <t>69,02; 81,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,97; 80,17</t>
+          <t>71,04; 83,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,24; 94,39</t>
+          <t>79,07; 89,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,09; 91,94</t>
+          <t>71,62; 86,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,88; 81,77</t>
+          <t>69,0; 82,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,09; 84,42</t>
+          <t>66,23; 80,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,98; 90,1</t>
+          <t>84,51; 94,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>73,08; 87,1</t>
+          <t>69,65; 84,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71,26; 80,34</t>
+          <t>70,97; 79,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71,16; 80,15</t>
+          <t>71,21; 80,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83,39; 91,02</t>
+          <t>83,75; 90,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,27; 87,55</t>
+          <t>73,59; 83,97</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>76,11%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>69,64%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96,01%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87,86%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>74,62%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>62,32%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>92,09%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>84,55%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,22; 82,01</t>
+          <t>67,74; 83,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,08; 71,32</t>
+          <t>60,43; 77,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,49; 96,62</t>
+          <t>90,74; 99,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75,75; 91,1</t>
+          <t>81,29; 93,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,13; 83,39</t>
+          <t>64,94; 82,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,89; 78,25</t>
+          <t>51,79; 71,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,05; 98,97</t>
+          <t>85,14; 96,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,52; 93,51</t>
+          <t>75,9; 90,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68,74; 80,53</t>
+          <t>69,05; 80,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58,73; 72,5</t>
+          <t>58,92; 72,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,53; 96,85</t>
+          <t>89,37; 96,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80,97; 91,02</t>
+          <t>80,58; 90,49</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80,6%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>47,9%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73,33%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>72,17%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>79,6%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>56,96%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>87,09%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>68,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>80,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>47,9%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,93; 79,53</t>
+          <t>59,19; 76,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,82; 86,44</t>
+          <t>71,68; 87,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,85; 65,43</t>
+          <t>39,07; 58,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,14; 93,21</t>
+          <t>44,33; 86,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,42; 75,84</t>
+          <t>63,58; 79,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,84; 87,18</t>
+          <t>70,89; 86,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,63; 56,63</t>
+          <t>47,67; 66,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,43; 86,82</t>
+          <t>77,32; 92,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63,9; 75,63</t>
+          <t>63,71; 75,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74,6; 84,9</t>
+          <t>74,47; 84,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44,24; 59,7</t>
+          <t>45,74; 58,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56,87; 87,58</t>
+          <t>62,55; 88,04</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>76,16%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>67,21%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>83,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>80,63%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>97,02%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24,95%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>76,16%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>67,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,83; 91,13</t>
+          <t>63,82; 84,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,74; 88,54</t>
+          <t>54,95; 78,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,91; 100,0</t>
+          <t>89,56; 98,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,88; 37,63</t>
+          <t>17,27; 38,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,9; 84,44</t>
+          <t>72,38; 91,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,02; 78,31</t>
+          <t>68,09; 89,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,8; 98,71</t>
+          <t>89,17; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,69; 41,41</t>
+          <t>15,67; 39,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,44; 85,75</t>
+          <t>72,93; 86,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65,35; 81,12</t>
+          <t>65,62; 80,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91,81; 98,6</t>
+          <t>92,63; 98,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,54; 34,98</t>
+          <t>19,26; 34,48</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>79,67%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61,61%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>91,35%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>79,09%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>63,59%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>95,77%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>79,67%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,19%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69,55; 87,46</t>
+          <t>70,91; 87,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51,92; 73,59</t>
+          <t>50,86; 71,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88,04; 98,85</t>
+          <t>90,12; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,12; 97,32</t>
+          <t>84,34; 96,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70,8; 87,03</t>
+          <t>69,0; 86,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,56; 71,76</t>
+          <t>51,43; 73,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,7; 100,0</t>
+          <t>88,24; 98,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84,89; 96,61</t>
+          <t>84,65; 97,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73,51; 85,22</t>
+          <t>72,81; 85,16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55,4; 70,26</t>
+          <t>54,4; 69,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92,41; 98,74</t>
+          <t>92,22; 98,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>87,51; 95,65</t>
+          <t>86,66; 95,5</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>85,3%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>73,89%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>85,75%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>81,65%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>70,87%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>91,96%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>79,44%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>85,3%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,4%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>76,1; 86,55</t>
+          <t>79,8; 89,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63,93; 77,89</t>
+          <t>68,03; 79,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,88; 94,93</t>
+          <t>89,9; 96,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73,34; 85,28</t>
+          <t>79,57; 90,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,27; 89,83</t>
+          <t>75,83; 87,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,38; 79,87</t>
+          <t>63,95; 76,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,3; 96,19</t>
+          <t>87,77; 95,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>76,62; 89,62</t>
+          <t>71,71; 84,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>79,52; 86,93</t>
+          <t>79,79; 86,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67,49; 76,17</t>
+          <t>67,86; 76,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89,78; 94,76</t>
+          <t>90,08; 95,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,23; 86,55</t>
+          <t>78,29; 86,36</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>73,75%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>83,29%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>67,62%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>76,99%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>86,56%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>94,84%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>73,38%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>73,75%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>83,29%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>71,53; 81,9</t>
+          <t>68,15; 78,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81,72; 90,66</t>
+          <t>78,18; 87,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91,9; 97,23</t>
+          <t>90,81; 96,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66,38; 79,34</t>
+          <t>60,36; 73,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>67,89; 78,92</t>
+          <t>71,26; 81,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,38; 87,34</t>
+          <t>81,61; 90,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,44; 96,25</t>
+          <t>91,75; 97,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,83; 73,92</t>
+          <t>66,87; 80,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71,48; 78,89</t>
+          <t>71,68; 79,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81,6; 88,08</t>
+          <t>81,52; 88,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91,98; 96,06</t>
+          <t>92,41; 96,15</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>64,88; 74,3</t>
+          <t>65,82; 75,15</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76,68%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74,72%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>77,6%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>75,25%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>87,19%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>76,68%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>74,72%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>75,03; 80,03</t>
+          <t>73,77; 79,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72,53; 77,8</t>
+          <t>71,91; 77,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84,71; 89,13</t>
+          <t>83,79; 88,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74,08; 80,84</t>
+          <t>71,89; 78,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>74,05; 79,23</t>
+          <t>74,85; 79,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,88; 77,31</t>
+          <t>72,36; 78,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>83,67; 88,01</t>
+          <t>85,05; 89,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>71,76; 78,85</t>
+          <t>73,47; 79,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>75,32; 78,93</t>
+          <t>75,46; 79,02</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73,06; 76,72</t>
+          <t>73,08; 76,81</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85,09; 87,93</t>
+          <t>85,07; 87,98</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>73,96; 78,72</t>
+          <t>73,47; 78,1</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>72</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>45064</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40588</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44159</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48325</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>41421</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>40832</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>38360</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51968</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45064</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40588</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44159</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60937</t>
+          <t>41056</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>112906</t>
+          <t>89381</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35955; 45680</t>
+          <t>39146; 49543</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34356; 45468</t>
+          <t>33451; 46132</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32144; 43166</t>
+          <t>37472; 50338</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38231; 59513</t>
+          <t>42080; 53529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38933; 49806</t>
+          <t>36203; 45398</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34123; 46936</t>
+          <t>35365; 45723</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37282; 49524</t>
+          <t>32767; 43745</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53853; 66840</t>
+          <t>35600; 45899</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78743; 93049</t>
+          <t>79733; 93745</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73290; 90077</t>
+          <t>72925; 90436</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73810; 89863</t>
+          <t>74357; 90696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96399; 123536</t>
+          <t>80868; 96581</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82123</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86575</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>93816</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92891</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>76656</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>77521</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>93307</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>105500</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>82123</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86575</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93816</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>102802</t>
+          <t>78923</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>208301</t>
+          <t>171814</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69242; 82929</t>
+          <t>74606; 88528</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69075; 83952</t>
+          <t>78963; 93175</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87055; 97544</t>
+          <t>87206; 98976</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95855; 117368</t>
+          <t>82959; 100355</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74448; 88389</t>
+          <t>70078; 83644</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79019; 93846</t>
+          <t>69348; 84020</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87105; 99367</t>
+          <t>87337; 97493</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>93245; 111131</t>
+          <t>70620; 85899</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>149390; 168444</t>
+          <t>148787; 167599</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153623; 173023</t>
+          <t>153731; 174101</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178150; 194440</t>
+          <t>178910; 193861</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>194679; 223469</t>
+          <t>159868; 182419</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53527</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>49120</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67113</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52170</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>50443</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>42001</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>60875</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49268</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>53527</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>49120</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>67113</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59003</t>
+          <t>47901</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>108271</t>
+          <t>100072</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44088; 55437</t>
+          <t>47638; 58524</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35773; 48063</t>
+          <t>42628; 54971</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56514; 63873</t>
+          <t>63428; 69232</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44141; 53081</t>
+          <t>48266; 55606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>47913; 58645</t>
+          <t>43895; 56018</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41539; 55198</t>
+          <t>34901; 48134</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63646; 69187</t>
+          <t>56283; 63910</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54077; 62805</t>
+          <t>42927; 51456</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>94804; 111070</t>
+          <t>95242; 111693</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81012; 100001</t>
+          <t>81264; 100022</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121769; 131725</t>
+          <t>121552; 131540</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>101564; 114171</t>
+          <t>93420; 104916</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>81</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>53989</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65124</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38887</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>52914</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>54029</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>61901</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>43835</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>61089</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>53989</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65124</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38887</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56357</t>
+          <t>61358</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>117447</t>
+          <t>114271</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47110; 59536</t>
+          <t>46825; 60730</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55846; 67214</t>
+          <t>57914; 70358</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36058; 50355</t>
+          <t>31721; 47221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54813; 65378</t>
+          <t>31992; 62620</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47007; 59998</t>
+          <t>47598; 59774</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58851; 70439</t>
+          <t>55127; 66902</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30549; 45974</t>
+          <t>36688; 51150</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32370; 67832</t>
+          <t>54775; 65721</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>98384; 116443</t>
+          <t>98089; 116435</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>118282; 134619</t>
+          <t>118072; 134296</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69970; 94408</t>
+          <t>72336; 93092</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>84321; 129861</t>
+          <t>89448; 125905</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34152</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31424</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44452</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10681</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>34995</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>35399</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>41029</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8612</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>34152</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31424</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44452</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>19858</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30483; 38139</t>
+          <t>28617; 37887</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30179; 38872</t>
+          <t>25692; 36712</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38444; 42288</t>
+          <t>41509; 45753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5480; 12988</t>
+          <t>6834; 15230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28654; 37865</t>
+          <t>30294; 38227</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26190; 36611</t>
+          <t>29892; 39290</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41158; 45752</t>
+          <t>37707; 42288</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7609; 16861</t>
+          <t>5580; 14047</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61936; 74338</t>
+          <t>63228; 74829</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>59240; 73539</t>
+          <t>59485; 73276</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81375; 87395</t>
+          <t>82103; 87403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14697; 26318</t>
+          <t>14482; 25921</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>74</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>47586</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37119</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>54601</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>44708</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>44336</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>35603</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>50675</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>42917</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>47586</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>37119</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>54601</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>51448</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94365</t>
+          <t>87176</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38986; 49026</t>
+          <t>42357; 52012</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29068; 41198</t>
+          <t>30643; 43339</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46587; 52306</t>
+          <t>50630; 56182</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39295; 44928</t>
+          <t>41277; 47048</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>42293; 51987</t>
+          <t>38679; 48697</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30458; 43232</t>
+          <t>28793; 41167</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50958; 56182</t>
+          <t>46691; 52317</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>47699; 54282</t>
+          <t>38741; 44485</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85118; 98671</t>
+          <t>84300; 98608</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64394; 81665</t>
+          <t>63234; 81229</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>100821; 107726</t>
+          <t>100605; 107688</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>89569; 97901</t>
+          <t>82071; 90450</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>138</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>114589</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>133848</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>121226</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>105015</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>97817</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>126335</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>98914</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>114589</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>133848</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>131486</t>
+          <t>96217</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>230399</t>
+          <t>217443</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>97879; 111323</t>
+          <t>107200; 120849</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>88230; 107498</t>
+          <t>99143; 116011</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>120729; 130416</t>
+          <t>128942; 138161</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91309; 106176</t>
+          <t>112480; 127639</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>106479; 120668</t>
+          <t>97528; 112283</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>98195; 116402</t>
+          <t>88267; 106016</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>128086; 137958</t>
+          <t>120579; 130707</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>119534; 139814</t>
+          <t>87861; 103582</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>209097; 228596</t>
+          <t>209813; 227979</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>191522; 216126</t>
+          <t>192565; 217954</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>252089; 266084</t>
+          <t>252946; 266957</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>216632; 242800</t>
+          <t>206600; 227897</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>138</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>120994</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>142686</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>160560</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>107804</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>121577</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>142564</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>155710</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>96576</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>120994</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>142686</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>160560</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>105994</t>
+          <t>104145</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>202570</t>
+          <t>211948</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>112950; 129320</t>
+          <t>111797; 129085</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134593; 149317</t>
+          <t>133935; 149614</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>150874; 159624</t>
+          <t>155151; 164588</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>87369; 104429</t>
+          <t>96226; 117694</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>111373; 129473</t>
+          <t>112517; 129431</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>134270; 149623</t>
+          <t>134424; 148998</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>154512; 164434</t>
+          <t>150627; 159493</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>95372; 115906</t>
+          <t>93945; 113249</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>230123; 254002</t>
+          <t>230784; 254690</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>274198; 295986</t>
+          <t>273916; 295879</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>308153; 321838</t>
+          <t>309583; 322128</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>187133; 214282</t>
+          <t>197398; 225374</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>787</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>918</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>712</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>749</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>552024</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>560316</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>637436</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>530720</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>528471</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>533639</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>610128</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>514845</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>552024</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>560316</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>637436</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>579679</t>
+          <t>481245</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1094524</t>
+          <t>1011965</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>510969; 544993</t>
+          <t>531032; 569418</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>514352; 551741</t>
+          <t>539212; 577892</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>592800; 623724</t>
+          <t>621765; 653037</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>493501; 538549</t>
+          <t>503826; 550622</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>533092; 570402</t>
+          <t>509734; 544114</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>538961; 579701</t>
+          <t>513145; 553843</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>620838; 653042</t>
+          <t>595178; 622956</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>546755; 600807</t>
+          <t>462596; 497545</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1055193; 1105701</t>
+          <t>1057138; 1107039</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1065909; 1119379</t>
+          <t>1066253; 1120739</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1226851; 1267830</t>
+          <t>1226504; 1268462</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1056234; 1124260</t>
+          <t>977554; 1039155</t>
         </is>
       </c>
     </row>
